--- a/out/רשימת גבייה 7.10.2026.xlsx
+++ b/out/רשימת גבייה 7.10.2026.xlsx
@@ -1213,12 +1213,10 @@
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>ענק הבשר</t>

--- a/out/רשימת גבייה 7.10.2026.xlsx
+++ b/out/רשימת גבייה 7.10.2026.xlsx
@@ -1215,7 +1215,7 @@
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n">
-        <v>15</v>
+        <v>15000</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
